--- a/BBDetections.xlsx
+++ b/BBDetections.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alex/Documents/GitHub/BackyardBirds/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelseymccune/Documents/GitHub/BackyardBirds/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B82620-5A1A-BA44-8574-C934B1D0595B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F707B99-1447-C342-9D15-D754EDE7D158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{AFD5C794-3CDA-7B4E-95CA-1FB2B4E8F527}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18800" xr2:uid="{AFD5C794-3CDA-7B4E-95CA-1FB2B4E8F527}"/>
   </bookViews>
   <sheets>
     <sheet name="BBDetections" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10913" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10916" uniqueCount="201">
   <si>
     <t>Site</t>
   </si>
@@ -1131,7 +1131,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1142,6 +1142,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="21" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -69408,13 +69409,27 @@
       <c r="I2951" s="6"/>
     </row>
     <row r="2952" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2952" s="7"/>
-      <c r="B2952" s="7"/>
-      <c r="C2952" s="7"/>
-      <c r="D2952" s="7"/>
-      <c r="E2952" s="7"/>
-      <c r="F2952" s="7"/>
-      <c r="G2952" s="7"/>
+      <c r="A2952" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2952" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2952" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2952" s="7">
+        <v>30.8</v>
+      </c>
+      <c r="E2952" s="10">
+        <v>46118</v>
+      </c>
+      <c r="F2952" s="8">
+        <v>0.66563657407407406</v>
+      </c>
+      <c r="G2952" s="7">
+        <v>1</v>
+      </c>
       <c r="H2952" s="7"/>
       <c r="I2952" s="6"/>
     </row>
